--- a/artfynd/A 18705-2022 artfynd.xlsx
+++ b/artfynd/A 18705-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 18705-2022 artfynd.xlsx
+++ b/artfynd/A 18705-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1944815</v>
+        <v>258589</v>
       </c>
       <c r="B2" t="n">
-        <v>78568</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Öster Brassberget, mellan kraftledningar (väst om Bergtjärn)., Hls</t>
+          <t>Brassbergsmyran, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539106.742630115</v>
+        <v>538948</v>
       </c>
       <c r="R2" t="n">
-        <v>6896898.74913759</v>
+        <v>6897028</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2009-09-02</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-09-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2009-09-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-09-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,12 +763,12 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Fint lövbrännebestånd</t>
+          <t>Grandominerad skog med klen asp</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Två sälgar, rikligt med lunglav</t>
+          <t>Sälg 15 cm</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -790,7 +779,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars, Bengt Oldhammer</t>
+          <t>Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -801,53 +790,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1997235</v>
+        <v>107569747</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Brassbergsmyran, Hls</t>
+          <t>Brassberget, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>539054.5526221115</v>
+        <v>538944</v>
       </c>
       <c r="R3" t="n">
-        <v>6896965.355580899</v>
+        <v>6897042</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,22 +855,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2012-09-26</t>
+          <t>2023-03-23</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2012-09-26</t>
+          <t>2023-03-23</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,83 +881,64 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Grandominerad men lövrik skog</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Sälglåga, fälld nära kraftledningsgata</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Åtgärdsprogram för hotade arter</t>
-        </is>
-      </c>
+          <t>Isak Vahlström, Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2072910</v>
+        <v>107569742</v>
       </c>
       <c r="B4" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Brassbergsmyran, Hls</t>
+          <t>Brassberget, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539054.5526221115</v>
+        <v>538913</v>
       </c>
       <c r="R4" t="n">
-        <v>6896965.355580899</v>
+        <v>6897101</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,22 +962,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2012-09-26</t>
+          <t>2023-03-23</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2012-09-26</t>
+          <t>2023-03-23</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,83 +988,64 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Grandominerad men lövrik skog, intill ledningsgata</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Sälglåga, fälld nära kraftledningsgata</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Åtgärdsprogram för hotade arter</t>
-        </is>
-      </c>
+          <t>Isak Vahlström, Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1997234</v>
+        <v>107569749</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Brassbergsmyran, Hls</t>
+          <t>Brassberget, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>539060.7095074151</v>
+        <v>538977</v>
       </c>
       <c r="R5" t="n">
-        <v>6896958.425786681</v>
+        <v>6897012</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1123,27 +1069,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2012-09-26</t>
+          <t>2023-03-23</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2012-09-26</t>
+          <t>2023-03-23</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,83 +1095,64 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Grandominerad men lövrik skog</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Sälglåga utan bark</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Åtgärdsprogram för hotade arter</t>
-        </is>
-      </c>
+          <t>Isak Vahlström, Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1997233</v>
+        <v>107569755</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Brassbergsmyran, Hls</t>
+          <t>Brassberget, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539081.7084854279</v>
+        <v>539130</v>
       </c>
       <c r="R6" t="n">
-        <v>6896961.46973133</v>
+        <v>6896939</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1254,22 +1176,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2012-09-26</t>
+          <t>2023-03-23</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2012-09-26</t>
+          <t>2023-03-23</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,87 +1202,64 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Grandominerad men lövrik skog</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Asp 30-40 cm</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Åtgärdsprogram för hotade arter</t>
-        </is>
-      </c>
+          <t>Isak Vahlström, Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>258589</v>
+        <v>107569738</v>
       </c>
       <c r="B7" t="n">
-        <v>89952</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>760</v>
+        <v>6437</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Brassbergsmyran, Hls</t>
+          <t>Brassberget, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>538948.1891960427</v>
+        <v>538754</v>
       </c>
       <c r="R7" t="n">
-        <v>6897028.067720329</v>
+        <v>6897044</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1384,22 +1283,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2012-09-26</t>
+          <t>2023-03-23</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2012-09-26</t>
+          <t>2023-03-23</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1410,67 +1309,48 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med klen asp</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Sälg 15 cm</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Åtgärdsprogram för hotade arter</t>
-        </is>
-      </c>
+          <t>Isak Vahlström, Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>107569746</v>
+        <v>107569739</v>
       </c>
       <c r="B8" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1480,10 +1360,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>538923.8166075038</v>
+        <v>538791</v>
       </c>
       <c r="R8" t="n">
-        <v>6897033.853634592</v>
+        <v>6897081</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1515,7 +1395,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1525,7 +1405,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1552,53 +1432,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>107569747</v>
+        <v>1944815</v>
       </c>
       <c r="B9" t="n">
-        <v>89952</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Brassberget, Hls</t>
+          <t>Öster Brassberget, mellan kraftledningar (väst om Bergtjärn)., Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>538943.8211877134</v>
+        <v>539107</v>
       </c>
       <c r="R9" t="n">
-        <v>6897042.019234723</v>
+        <v>6896899</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1622,22 +1497,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:44</t>
+          <t>2009-09-02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:44</t>
+          <t>2009-09-02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1648,31 +1513,40 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Fint lövbrännebestånd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Två sälgar, rikligt med lunglav</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Aron Dynesius</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Lars-Ove Wikars, Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>107569755</v>
+        <v>1997233</v>
       </c>
       <c r="B10" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1680,37 +1554,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Brassberget, Hls</t>
+          <t>Brassbergsmyran, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539130.1126433859</v>
+        <v>539082</v>
       </c>
       <c r="R10" t="n">
-        <v>6896939.160931129</v>
+        <v>6896961</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1734,22 +1608,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:34</t>
+          <t>2012-09-26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:34</t>
+          <t>2012-09-26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1760,69 +1624,78 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Grandominerad men lövrik skog</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Asp 30-40 cm</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Aron Dynesius</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Lars-Ove Wikars</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>107569739</v>
+        <v>1997234</v>
       </c>
       <c r="B11" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Brassberget, Hls</t>
+          <t>Brassbergsmyran, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>538791.4637094707</v>
+        <v>539061</v>
       </c>
       <c r="R11" t="n">
-        <v>6897080.867268534</v>
+        <v>6896958</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1846,22 +1719,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2012-09-26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2012-09-26</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1872,31 +1740,40 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Grandominerad men lövrik skog</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Sälglåga utan bark</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Aron Dynesius</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Lars-Ove Wikars</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>107569745</v>
+        <v>1997235</v>
       </c>
       <c r="B12" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,17 +1801,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Brassberget, Hls</t>
+          <t>Brassbergsmyran, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>538918.6757011655</v>
+        <v>539055</v>
       </c>
       <c r="R12" t="n">
-        <v>6897033.794253739</v>
+        <v>6896965</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1958,22 +1835,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>15:47</t>
+          <t>2012-09-26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>15:47</t>
+          <t>2012-09-26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1984,31 +1851,40 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Grandominerad men lövrik skog</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Sälglåga, fälld nära kraftledningsgata</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Aron Dynesius</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Lars-Ove Wikars</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>107569748</v>
+        <v>1997477</v>
       </c>
       <c r="B13" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,17 +1912,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Brassberget, Hls</t>
+          <t>Brassbergsmyran, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>538977.3541966603</v>
+        <v>538841</v>
       </c>
       <c r="R13" t="n">
-        <v>6897012.069211906</v>
+        <v>6897035</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2070,22 +1946,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:41</t>
+          <t>2012-09-26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:41</t>
+          <t>2012-09-26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2096,31 +1962,40 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Lövbränna</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Aspstubbe 14 cm</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Aron Dynesius</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Lars-Ove Wikars</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>107569756</v>
+        <v>107569741</v>
       </c>
       <c r="B14" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2152,10 +2027,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539130.1126433859</v>
+        <v>538826</v>
       </c>
       <c r="R14" t="n">
-        <v>6896939.160931129</v>
+        <v>6897108</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2187,7 +2062,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2197,7 +2072,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2224,15 +2099,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>107569754</v>
+        <v>107569745</v>
       </c>
       <c r="B15" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,10 +2134,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>539102.5395484278</v>
+        <v>538919</v>
       </c>
       <c r="R15" t="n">
-        <v>6896978.980878366</v>
+        <v>6897034</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2299,7 +2169,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2309,7 +2179,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2336,15 +2206,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>107569710</v>
+        <v>107569746</v>
       </c>
       <c r="B16" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2352,42 +2217,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Brassberget, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>539063</v>
+        <v>538924</v>
       </c>
       <c r="R16" t="n">
-        <v>6896864</v>
+        <v>6897034</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2419,7 +2276,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2429,7 +2286,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2456,15 +2313,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>107569749</v>
+        <v>107569748</v>
       </c>
       <c r="B17" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2472,21 +2324,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2496,10 +2348,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>538977.3541966603</v>
+        <v>538977</v>
       </c>
       <c r="R17" t="n">
-        <v>6897012.069211906</v>
+        <v>6897012</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2565,6 +2417,1433 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>107569752</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Brassberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>538986</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6897034</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>107569754</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Brassberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>539103</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6896979</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>107569756</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Brassberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>539130</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6896939</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2072910</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Brassbergsmyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>539055</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6896965</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2012-09-26</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2012-09-26</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Grandominerad men lövrik skog, intill ledningsgata</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Sälglåga, fälld nära kraftledningsgata</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Lars-Ove Wikars</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Lars-Ove Wikars</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>107569750</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Brassberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>538986</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6897030</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>107569737</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78334</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Brassberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>538758</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6897050</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>107569736</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Brassberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>538766</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6897041</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>107569740</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Brassberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>538828</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6897086</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>107569710</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Brassberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>539063</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6896864</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>107569743</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Brassberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>538920</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6897099</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>107569744</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Brassberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>538919</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6897101</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>3066358</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Brassbergsmyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>538769</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6897036</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2012-09-26</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2012-09-26</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Lövbränna</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Intill liten bäck</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Lars-Ove Wikars</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Lars-Ove Wikars</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>107569735</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Brassberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>538757</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6897041</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18705-2022 artfynd.xlsx
+++ b/artfynd/A 18705-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/258589</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107569747</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107569742</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107569749</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1215,6 +1240,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107569755</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1322,6 +1352,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107569738</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1429,6 +1464,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107569739</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1540,6 +1580,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1944815</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1651,6 +1696,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1997233</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1767,6 +1817,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1997234</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1878,6 +1933,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1997235</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1989,6 +2049,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1997477</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2096,6 +2161,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107569741</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2203,6 +2273,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107569745</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2310,6 +2385,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107569746</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2417,6 +2497,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107569748</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2524,6 +2609,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107569752</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2631,6 +2721,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107569754</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2738,6 +2833,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107569756</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2849,6 +2949,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2072910</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2956,6 +3061,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107569750</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3063,6 +3173,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107569737</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3175,6 +3290,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107569736</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3287,6 +3407,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107569740</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3402,6 +3527,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107569710</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3514,6 +3644,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107569743</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3626,6 +3761,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107569744</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3737,6 +3877,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3066358</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3844,8 +3989,44 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107569735</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>